--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_11_8.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_11_8.xlsx
@@ -517,657 +517,657 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9993257198063945</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6909732240352646</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9971792942352391</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9996780725431837</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9981828564346047</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004002818503119724</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1834516434743036</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001829867918952363</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0001166121695636539</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009732400442580084</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008567284264467534</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0200070450169927</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000265290567976</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O2" t="n">
-        <v>0.02085878634365875</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P2" t="n">
-        <v>185.6466832664171</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q2" t="n">
-        <v>289.2511283802141</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_1</t>
+          <t>model_11_8_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9994183780288809</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6894597033962572</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9976818776802266</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9994354296175765</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9984051790586861</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003452759268171958</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1843501347063057</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001503828480855454</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0002045050081061434</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0008541667444807985</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008075333093961679</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0185816018366877</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000228834873883</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O3" t="n">
-        <v>0.019372659096094</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P3" t="n">
-        <v>185.9423333454338</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q3" t="n">
-        <v>289.5467784592308</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_2</t>
+          <t>model_11_8_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.99948445200601</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6880498067579515</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9980895669734267</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9991458673802446</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9985541646100732</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003060515597462271</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1851871102551675</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001239349438820271</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000309393485320606</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007743718909606482</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007632823439321331</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01749432935971617</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000202838555012</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01823909917881348</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P4" t="n">
-        <v>186.183513948606</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q4" t="n">
-        <v>289.7879590624031</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_3</t>
+          <t>model_11_8_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9995293499556162</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6867418663870477</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9984191754093048</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9988242474614407</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9986450236249151</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002793981973695689</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1859635601594181</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001025523555183463</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0004258942550204753</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0007257089051019691</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00723472958282386</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01671520856494375</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000185173787954</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O5" t="n">
-        <v>0.01742680959880522</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P5" t="n">
-        <v>186.3657451259066</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q5" t="n">
-        <v>289.9701902397037</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_4</t>
+          <t>model_11_8_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9995575520254273</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6855324682083443</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9986846934662895</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9984827535735454</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9986903454574474</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002626562304636545</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1866815111615774</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008532748291912507</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0005495939964281711</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0007014350815365156</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006876535621441601</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M6" t="n">
-        <v>0.01620667240563758</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000174077891635</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01689662400238241</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P6" t="n">
-        <v>186.4893289786024</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q6" t="n">
-        <v>290.0937740923994</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_5</t>
+          <t>model_11_8_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9995727702908473</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6844179198888554</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9988978055375967</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9981315818176186</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F7" t="n">
-        <v>0.998700658909635</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0002536220107155179</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1873431551900065</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007150232797746805</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0006767993636034398</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0006959113216890602</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006554027352348489</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01592551445685564</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000168090377372</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01660349657764363</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P7" t="n">
-        <v>186.5593310922505</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q7" t="n">
-        <v>290.1637762060475</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_6</t>
+          <t>model_11_8_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9995780163567558</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6833936225368455</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9990681596697215</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9977787004248181</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9986845036786893</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0002505077193740023</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1879512223455013</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0006045099589134549</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0008046240145980408</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0007045638673547143</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006263697118617154</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01582743565376282</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N8" t="n">
-        <v>1.00016602635144</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01650124235685204</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P8" t="n">
-        <v>186.5840416440998</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q8" t="n">
-        <v>290.1884867578968</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_7</t>
+          <t>model_11_8_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9995757445977406</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6824543351029433</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9992038096266536</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9974302884199006</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9986488323839009</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0002518563336603293</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1885088239413701</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0005165101726549275</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J9" t="n">
-        <v>0.000930829713848639</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0007236689800050144</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L9" t="n">
-        <v>0.006002266199055079</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01586998215690015</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000166920158266</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01654560015271134</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P9" t="n">
-        <v>186.5733034750935</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q9" t="n">
-        <v>290.1777485888905</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_8</t>
+          <t>model_11_8_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.999567915943152</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6815948408714523</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D10" t="n">
-        <v>0.999311310444729</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9970910088208639</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9985992018774835</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0002565037612043713</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1890190568454007</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000446771492103768</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001053727370742015</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0007502504770215635</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L10" t="n">
-        <v>0.005766762473239826</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01601573480063813</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000170000284661</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01669755778824281</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P10" t="n">
-        <v>186.5367344597923</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q10" t="n">
-        <v>290.1411795735894</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_9</t>
+          <t>model_11_8_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.999556101099218</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6808100443060872</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9993960414239786</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9967643583783578</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9985400648632904</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0002635175629382396</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1894849459880479</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0003918042202218979</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001172050353088061</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0007819235442500753</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L11" t="n">
-        <v>0.005554785618460702</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01623322404632671</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000174648747849</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01692430600138515</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P11" t="n">
-        <v>186.482781079374</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q11" t="n">
-        <v>290.087226193171</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_10</t>
+          <t>model_11_8_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9995415647068316</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6800947111680622</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9994624652244876</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9964528695263062</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F12" t="n">
-        <v>0.998474954000559</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0002721469933982329</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1899095986395621</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0003487133090305784</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J12" t="n">
-        <v>0.001284881334303076</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0008167961322685166</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005363822496811781</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01649687829252046</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000180367984197</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0171991845546789</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P12" t="n">
-        <v>186.4183364414713</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q12" t="n">
-        <v>290.0227815552684</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_11</t>
+          <t>model_11_8_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9995252825161071</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C13" t="n">
-        <v>0.6794434478646645</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D13" t="n">
-        <v>0.999514200202965</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9961580874494662</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9984066070188544</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0002818128051664039</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1902962166695688</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0003151514329263159</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J13" t="n">
-        <v>0.001391660600255574</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0008534019463416227</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005191708560211732</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01678728105341672</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000186774092023</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0175019503623231</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P13" t="n">
-        <v>186.3485350378264</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q13" t="n">
-        <v>289.9529801516234</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="14">
@@ -1177,657 +1177,657 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9995079859193419</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6788512438663346</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9995541290782828</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9958807930776122</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9983370107114227</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0002920808121802944</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1906477745448582</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0002892484944147048</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J14" t="n">
-        <v>0.001492105273814869</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0008906768841147869</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005036841354876318</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01709037191462767</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000193579310423</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01781794442898038</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P14" t="n">
-        <v>186.2769600798864</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q14" t="n">
-        <v>289.8814051936835</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_13</t>
+          <t>model_11_8_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.999490273283959</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6783133556834171</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D15" t="n">
-        <v>0.999584669577852</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9956214900856529</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9982678252860185</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0003025957976895541</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1909670882057976</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0002694360485054223</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J15" t="n">
-        <v>0.001586032908213538</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0009277317584597131</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L15" t="n">
-        <v>0.004901000062132711</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M15" t="n">
-        <v>0.01739528090286426</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000200548216147</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01813583402409482</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P15" t="n">
-        <v>186.2062252881019</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q15" t="n">
-        <v>289.810670401899</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_14</t>
+          <t>model_11_8_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9994725691327709</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6778254388980611</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9996077588156519</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9953800334459729</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9982001520228827</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0003131057466143328</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1912567366864926</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0002544574371057641</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J16" t="n">
-        <v>0.001673496036978939</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0009639767370423513</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L16" t="n">
-        <v>0.004779029629059328</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M16" t="n">
-        <v>0.01769479433659326</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000207513783828</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01844809836477594</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P16" t="n">
-        <v>186.137939151748</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q16" t="n">
-        <v>289.7423842655451</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_15</t>
+          <t>model_11_8_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.999455214352974</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C17" t="n">
-        <v>0.6773831772604719</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9996249397438191</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9951562946057648</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9981348971302166</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0003234082935891802</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1915192822992735</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0002433117055432295</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J17" t="n">
-        <v>0.001754541225949015</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0009989264657461222</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004669206762032804</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M17" t="n">
-        <v>0.01798355619973925</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000214341893912</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01874915341825553</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P17" t="n">
-        <v>186.0731899323238</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q17" t="n">
-        <v>289.6776350461209</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_16</t>
+          <t>model_11_8_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9994384269828296</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6769827114293131</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9996374650718818</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9949496105851777</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9980725986991998</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0003333740016835765</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1917570161158725</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0002351861873545557</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J18" t="n">
-        <v>0.00182940862711188</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>0.001032292749464529</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L18" t="n">
-        <v>0.004570299017614245</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0182585322981771</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000220946760854</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01903583581848287</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P18" t="n">
-        <v>186.0124911400831</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q18" t="n">
-        <v>289.6169362538801</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_17</t>
+          <t>model_11_8_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9994223616043975</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6766201664180278</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9996463646909997</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9947591500819506</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9980135643915867</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0003429111043091035</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1919722384957005</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0002294127643630099</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J19" t="n">
-        <v>0.001898399364084574</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K19" t="n">
-        <v>0.001063910808295002</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L19" t="n">
-        <v>0.004481168419753427</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M19" t="n">
-        <v>0.01851785906386328</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000227267565483</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01930620266146471</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P19" t="n">
-        <v>185.9560786309989</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q19" t="n">
-        <v>289.5605237447959</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_18</t>
+          <t>model_11_8_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9994071303591493</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C20" t="n">
-        <v>0.6762922359092649</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9996524196112663</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9945842231370866</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9979580775452142</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0003519530294439652</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1921669122115625</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0002254847742528467</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J20" t="n">
-        <v>0.001961763361543749</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K20" t="n">
-        <v>0.001093628889930257</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L20" t="n">
-        <v>0.004401008055577746</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M20" t="n">
-        <v>0.01876041122800791</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000233260186564</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01955908077338918</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P20" t="n">
-        <v>185.9040256606992</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q20" t="n">
-        <v>289.5084707744963</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_19</t>
+          <t>model_11_8_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9993927875225539</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6759957751128465</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9996563024071246</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9944238185922024</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9979061891078493</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0003604675568252453</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1923429041467561</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0002229658998400509</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J21" t="n">
-        <v>0.002019866892605706</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00112141970736436</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L21" t="n">
-        <v>0.004328772640705958</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01898598316720115</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000238903269815</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01979425577703216</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P21" t="n">
-        <v>185.8562172004519</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q21" t="n">
-        <v>289.460662314249</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_20</t>
+          <t>model_11_8_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9993793655001394</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6757278474953534</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9996585028035232</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9942771046853861</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9978579240452012</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0003684354491316588</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1925019575543704</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0002215384433398902</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J22" t="n">
-        <v>0.002073011247387384</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K22" t="n">
-        <v>0.001147269889266475</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L22" t="n">
-        <v>0.004263670580624993</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M22" t="n">
-        <v>0.01919467241532553</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000244184065519</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0200118293584955</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P22" t="n">
-        <v>185.8124900672844</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q22" t="n">
-        <v>289.4169351810815</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_21</t>
+          <t>model_11_8_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9993668653185885</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6754858463828737</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9996594230733629</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9941431317765947</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9978131705890949</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0003758560968799604</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1926456198686421</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0002209414394703737</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J23" t="n">
-        <v>0.002121540415142844</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K23" t="n">
-        <v>0.001171239297314959</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L23" t="n">
-        <v>0.004205238330793442</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M23" t="n">
-        <v>0.01938700845617911</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000249102169736</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0202123535427987</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P23" t="n">
-        <v>185.7726084177894</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q23" t="n">
-        <v>289.3770535315865</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_22</t>
+          <t>model_11_8_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.999355291765876</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6752673658468045</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D24" t="n">
-        <v>0.999659431351858</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9940210995075434</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9977719058519849</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0003827266577215601</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1927753193527205</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0002209360689872984</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J24" t="n">
-        <v>0.002165744310615428</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K24" t="n">
-        <v>0.001193340189801363</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L24" t="n">
-        <v>0.004152465369390277</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M24" t="n">
-        <v>0.01956340097533044</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000253655698672</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O24" t="n">
-        <v>0.02039625545667316</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P24" t="n">
-        <v>185.7363790219816</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q24" t="n">
-        <v>289.3408241357786</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_11_8_23</t>
+          <t>model_11_8_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9993445953824586</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6750701610406475</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9996587248757233</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9939099882216461</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9977338948070302</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0003890764929778948</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1928923886444593</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0002213943791133045</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J25" t="n">
-        <v>0.002205992285235628</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>0.00121369844424997</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L25" t="n">
-        <v>0.004105011929546519</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M25" t="n">
-        <v>0.01972502200196225</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N25" t="n">
-        <v>1.00025786411182</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O25" t="n">
-        <v>0.02056475702501033</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P25" t="n">
-        <v>185.7034691872619</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q25" t="n">
-        <v>289.3079143010589</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9993347446516846</v>
+        <v>0.99990445773345</v>
       </c>
       <c r="C26" t="n">
-        <v>0.6748921729668284</v>
+        <v>0.639493994001567</v>
       </c>
       <c r="D26" t="n">
-        <v>0.999657542866061</v>
+        <v>0.999598506389254</v>
       </c>
       <c r="E26" t="n">
-        <v>0.993808929312002</v>
+        <v>0.9997711616501357</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9976990141925981</v>
+        <v>0.9997096873414572</v>
       </c>
       <c r="G26" t="n">
-        <v>0.000394924312294721</v>
+        <v>5.671801663509071e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1929980500537629</v>
+        <v>0.2140119382092531</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0002221611806662257</v>
+        <v>0.0001913393493978302</v>
       </c>
       <c r="J26" t="n">
-        <v>0.002242598975525046</v>
+        <v>5.438693793884891e-05</v>
       </c>
       <c r="K26" t="n">
-        <v>0.001232380078095636</v>
+        <v>0.0001228631436683395</v>
       </c>
       <c r="L26" t="n">
-        <v>0.004062294910454699</v>
+        <v>0.001757617705300685</v>
       </c>
       <c r="M26" t="n">
-        <v>0.01987270269225404</v>
+        <v>0.007531136476992746</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000261739809173</v>
+        <v>1.000037590399954</v>
       </c>
       <c r="O26" t="n">
-        <v>0.02071872478802902</v>
+        <v>0.007851752548420023</v>
       </c>
       <c r="P26" t="n">
-        <v>185.6736328517346</v>
+        <v>189.5548372879966</v>
       </c>
       <c r="Q26" t="n">
-        <v>289.2780779655316</v>
+        <v>293.1592824017936</v>
       </c>
     </row>
   </sheetData>
